--- a/output/pdf_financials_xlsx/TPZ.xlsx
+++ b/output/pdf_financials_xlsx/TPZ.xlsx
@@ -3900,7 +3900,11 @@
           <t>Prepaids and deposits 721</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>
@@ -5594,7 +5598,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="n">
         <v>0.785</v>
       </c>
@@ -6748,7 +6756,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TPZ.xlsx
+++ b/output/pdf_financials_xlsx/TPZ.xlsx
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>3.461</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.461</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="35">
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>3.461</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.461</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="37">
@@ -1732,13 +1732,13 @@
         <v>6.997</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>13.038</v>
+        <v>9.577</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>13.038</v>
+        <v>9.577</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>11.536</v>
+        <v>11.389</v>
       </c>
     </row>
     <row r="49">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">

--- a/output/pdf_financials_xlsx/TPZ.xlsx
+++ b/output/pdf_financials_xlsx/TPZ.xlsx
@@ -3097,19 +3097,19 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.197</v>
       </c>
     </row>
     <row r="111">
@@ -7977,7 +7977,11 @@
           <t>Accretion expense (note 10)</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E110" s="5" t="n">
         <v>0.091</v>
       </c>
@@ -8117,7 +8121,11 @@
           <t>Deferred income tax expense (note 15)</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E114" s="5" t="n">
         <v>6.653</v>
       </c>
